--- a/tests/fixtures/bra_ntu_sample.xlsx
+++ b/tests/fixtures/bra_ntu_sample.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4A.1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A.1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -628,4 +629,97 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tillbaka till tabellforteckningen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tabell 5A:1. Fortroende for rattsvasendet som helhet, enligt NTU 2007–2025. Andel (%) med ganska eller mycket stort fortroende.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2016*</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Konfidensintervall (95 %) undre grans 2018</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Konfidensintervall (95 %) ovre grans 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Samtliga 16–84 år</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>48.1095289388962</v>
+      </c>
+      <c r="C4" t="n">
+        <v>44.05565704563057</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46.79617284556913</v>
+      </c>
+      <c r="E4" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Samtliga - 16–19 år</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="n">
+        <v>47</v>
+      </c>
+      <c r="D5" t="n">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>